--- a/data/trans_orig/IP29B_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP29B_2023-Clase-trans_orig.xlsx
@@ -489,7 +489,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Meses con lactancia materna exclusiva</t>
+          <t>Meses con lactancia materna exclusiva (tasa de respuesta: 97,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,97; 12,12</t>
+          <t>7,93; 12,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,38; 11,14</t>
+          <t>7,36; 11,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,97; 10,74</t>
+          <t>8,0; 10,75</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,4; 9,21</t>
+          <t>6,47; 9,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,81; 10,75</t>
+          <t>6,81; 10,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,9; 9,09</t>
+          <t>6,88; 9,12</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,61; 14,89</t>
+          <t>8,83; 14,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,12; 10,53</t>
+          <t>6,08; 10,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,67; 11,69</t>
+          <t>7,64; 11,64</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,19; 9,92</t>
+          <t>7,25; 10,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,57; 11,68</t>
+          <t>8,45; 11,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,28; 10,51</t>
+          <t>8,24; 10,46</t>
         </is>
       </c>
     </row>
@@ -771,17 +771,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,5; 10,11</t>
+          <t>6,63; 10,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,05; 8,32</t>
+          <t>6,16; 8,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,68; 8,75</t>
+          <t>6,64; 8,63</t>
         </is>
       </c>
     </row>
@@ -821,17 +821,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,12; 13,88</t>
+          <t>5,97; 13,68</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,74; 14,59</t>
+          <t>6,57; 15,06</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,98; 12,38</t>
+          <t>6,94; 12,26</t>
         </is>
       </c>
     </row>
@@ -871,17 +871,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,93; 9,54</t>
+          <t>8,04; 9,69</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,02; 9,49</t>
+          <t>7,96; 9,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,25; 9,33</t>
+          <t>8,2; 9,31</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP29B_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP29B_2023-Clase-trans_orig.xlsx
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,93; 12,18</t>
+          <t>7,98; 12,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,36; 11,18</t>
+          <t>7,27; 10,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,0; 10,75</t>
+          <t>8,05; 10,78</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,47; 9,34</t>
+          <t>6,33; 8,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,81; 10,44</t>
+          <t>6,82; 10,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,88; 9,12</t>
+          <t>6,89; 9,04</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,83; 14,92</t>
+          <t>8,77; 14,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,08; 10,83</t>
+          <t>6,06; 11,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,64; 11,64</t>
+          <t>7,81; 11,6</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,25; 10,12</t>
+          <t>7,09; 9,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,45; 11,67</t>
+          <t>8,44; 11,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,24; 10,46</t>
+          <t>8,28; 10,37</t>
         </is>
       </c>
     </row>
@@ -771,17 +771,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,63; 10,3</t>
+          <t>6,58; 10,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,16; 8,47</t>
+          <t>6,05; 8,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,64; 8,63</t>
+          <t>6,67; 8,68</t>
         </is>
       </c>
     </row>
@@ -821,17 +821,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,97; 13,68</t>
+          <t>5,89; 13,46</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,57; 15,06</t>
+          <t>6,5; 14,47</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,94; 12,26</t>
+          <t>6,86; 12,57</t>
         </is>
       </c>
     </row>
@@ -871,17 +871,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>8,04; 9,69</t>
+          <t>8,0; 9,68</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,96; 9,55</t>
+          <t>7,97; 9,59</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,2; 9,31</t>
+          <t>8,17; 9,3</t>
         </is>
       </c>
     </row>
